--- a/event_planner_forms/025_pre_conference_survey--event_planner_forms.xlsx
+++ b/event_planner_forms/025_pre_conference_survey--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -892,12 +892,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>conference_satisfaction</t>
+          <t>conference_satisfaction_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Conference Satisfaction</t>
+          <t>Conference Satisfaction 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -984,12 +984,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>attendees_attendance</t>
+          <t>attendees_attendance_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Attendees Attendance</t>
+          <t>Attendees Attendance 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Details</t>
+          <t>Attendees Fees Details</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Details</t>
+          <t>Follow Up Details</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option11</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option11</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option12</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option12</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option13</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option13</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option14</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option14</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option15</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option15</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option16</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option16</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option17</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option17</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option18</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option18</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
